--- a/deploy/122_ENT_REPORTOS_CANASTA/67 CANASTA_REPORTOS.xlsx
+++ b/deploy/122_ENT_REPORTOS_CANASTA/67 CANASTA_REPORTOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\122_ENT_REPORTOS_CANASTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07BC810-EBE8-41B7-ACEB-7623A5CA9CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18BE725-E369-475C-87D0-484CEE06D509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11370" yWindow="6370" windowWidth="21830" windowHeight="13000" xr2:uid="{A59DD6BA-10F4-4938-9234-256BE7F1FD69}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{A59DD6BA-10F4-4938-9234-256BE7F1FD69}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
   <si>
     <t>FECHACONCERTACION</t>
   </si>
@@ -183,6 +183,54 @@
   </si>
   <si>
     <t>CAN0000000000000000000000000000000011</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000013</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000014</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000015</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000016</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000017</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000018</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000019</t>
+  </si>
+  <si>
+    <t>NIO0000000000000000000000000000000020</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000012</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000013</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000014</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000015</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000016</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000017</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000018</t>
+  </si>
+  <si>
+    <t>CAN0000000000000000000000000000000019</t>
   </si>
 </sst>
 </file>
@@ -556,14 +604,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820A80EF-6967-47F7-8431-30BAD99F9869}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46189</v>
       </c>
@@ -651,7 +699,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46189</v>
       </c>
@@ -695,7 +743,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46189</v>
       </c>
@@ -718,10 +766,10 @@
         <v>46387</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -739,7 +787,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46189</v>
       </c>
@@ -762,10 +810,10 @@
         <v>46387</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -783,7 +831,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46189</v>
       </c>
@@ -806,10 +854,10 @@
         <v>46387</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -827,7 +875,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46189</v>
       </c>
@@ -850,10 +898,10 @@
         <v>46387</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -871,7 +919,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46189</v>
       </c>
@@ -894,10 +942,10 @@
         <v>46387</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -915,7 +963,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46189</v>
       </c>
@@ -938,10 +986,10 @@
         <v>46387</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -959,7 +1007,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46189</v>
       </c>
@@ -982,10 +1030,10 @@
         <v>46387</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1003,7 +1051,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46189</v>
       </c>
@@ -1026,10 +1074,10 @@
         <v>46387</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="J11">
         <v>1</v>
